--- a/files/九龙-何文田-誉林.xlsx
+++ b/files/九龙-何文田-誉林.xlsx
@@ -606,7 +606,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -3276,14 +3276,14 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
         <v>15500000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>23628</v>
+        <v>23592</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3993,10 +3993,10 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>A | 656呎 (3房)
+          <t>A | 657呎 (3房)
 $1,550万
-$23,628/呎
-(26年-06月)</t>
+$23,592/呎
+(已售)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">

--- a/files/九龙-何文田-誉林.xlsx
+++ b/files/九龙-何文田-誉林.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="誉林 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="誉林" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +237,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3306,144 +3344,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>誉林 - 誉林 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>誉林 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>56 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>PH E</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>PH W</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>19&amp;20/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>PH E | 2449呎 (4+房)
 招标单位
@@ -3451,7 +3489,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>PH W | 2597呎 (4+房)
 招标单位
@@ -3460,13 +3498,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1386呎 (3房)
 招标单位
@@ -3474,7 +3512,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1340呎 (3房)
 招标单位
@@ -3482,19 +3520,19 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 1386呎 (3房)
 招标单位
@@ -3502,27 +3540,27 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1296呎 (3房)
-$3,874万
+$3874万
 $29,895/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 698呎 (3房)
 招标单位
@@ -3530,7 +3568,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 754呎 (3房)
 招标单位
@@ -3538,7 +3576,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 招标单位
@@ -3546,7 +3584,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $624万
@@ -3554,32 +3592,32 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 640呎 (3房)
-$1,550万
+$1550万
 $24,219/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr"/>
-      <c r="H9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,765万
+$1765万
 $25,250/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 754呎 (3房)
 招标单位
@@ -3587,15 +3625,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
-$1,165万
+$1165万
 $23,589/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $600万
@@ -3603,48 +3641,48 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 640呎 (3房)
-$1,483万
+$1483万
 $23,177/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr"/>
-      <c r="H10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,667万
+$1667万
 $23,854/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,796万
+$1796万
 $23,787/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
-$1,090万
+$1090万
 $22,065/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $568万
@@ -3652,48 +3690,48 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 640呎 (3房)
-$1,305万
+$1305万
 $20,392/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr"/>
-      <c r="H11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,634万
+$1634万
 $23,372/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,766万
+$1766万
 $23,389/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
-$1,085万
+$1085万
 $21,964/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $516万
@@ -3701,48 +3739,48 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 640呎 (3房)
-$1,292万
+$1292万
 $20,194/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,578万
+$1578万
 $22,579/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,669万
+$1669万
 $22,103/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
-$1,066万
+$1066万
 $21,571/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $503万
@@ -3750,40 +3788,40 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 640呎 (3房)
-$1,388万
+$1388万
 $21,681/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,562万
+$1562万
 $22,346/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,818万
+$1818万
 $24,083/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 $974万
@@ -3791,7 +3829,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $484万
@@ -3799,40 +3837,40 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 624呎 (3房)
-$1,277万
+$1277万
 $20,465/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr"/>
-      <c r="H14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,488万
+$1488万
 $21,289/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,634万
+$1634万
 $21,648/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 $933万
@@ -3840,7 +3878,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 260呎 (开放式)
 $479万
@@ -3848,40 +3886,40 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 672呎 (3房)
-$1,357万
+$1357万
 $20,199/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,472万
+$1472万
 $21,060/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,587万
+$1587万
 $21,021/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 $924万
@@ -3889,7 +3927,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 306呎 (1房)
 $587万
@@ -3897,33 +3935,33 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
-      <c r="H16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,485万
+$1485万
 $21,242/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,729万
+$1729万
 $22,905/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 $905万
@@ -3931,7 +3969,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 306呎 (1房)
 $594万
@@ -3939,33 +3977,33 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
-      <c r="H17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 699呎 (3房)
-$1,470万
+$1470万
 $21,029/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 755呎 (3房)
-$1,554万
+$1554万
 $20,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 $885万
@@ -3973,7 +4011,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 306呎 (1房)
 $562万
@@ -3981,25 +4019,25 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="20" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1,550万
+$1550万
 $23,592/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 713呎 (3房)
 招标单位
@@ -4007,7 +4045,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 879呎 (2房)
 招标单位
@@ -4015,14 +4053,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/九龙-何文田-誉林.xlsx
+++ b/files/九龙-何文田-誉林.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -644,10 +644,14 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -755,6 +779,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -805,6 +849,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -855,6 +919,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -905,6 +989,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -940,7 +1044,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -951,6 +1055,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>38744000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>29895</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1001,6 +1121,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1036,7 +1176,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1047,6 +1187,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>24219</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1082,7 +1238,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1093,6 +1249,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6238000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>23992</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1123,27 +1295,39 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>12403000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>25107</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>12403000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>25107</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1193,6 +1377,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1243,6 +1447,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1278,7 +1502,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1289,6 +1513,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>14833000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>23177</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1324,7 +1564,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1335,6 +1575,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>23077</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1370,7 +1626,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1381,6 +1637,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>11653000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>23589</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1431,6 +1703,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1466,7 +1758,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1477,6 +1769,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>25250</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1512,7 +1820,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1523,6 +1831,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>13051000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>20392</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1558,7 +1882,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1569,6 +1893,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5680000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>21846</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1604,7 +1944,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1615,6 +1955,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>10900000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>22065</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1650,7 +2006,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1661,6 +2017,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>17959000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>23787</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1696,7 +2068,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1707,6 +2079,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>16674000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>23854</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1742,7 +2130,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1753,6 +2141,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>12924000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>20194</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1788,7 +2192,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1799,6 +2203,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5160000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>19846</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1834,7 +2254,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1845,6 +2265,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>10850000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>21964</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1880,7 +2316,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1891,6 +2327,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>17659000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>23389</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1926,7 +2378,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1937,6 +2389,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>16337000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>23372</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1972,7 +2440,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1983,6 +2451,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>13876000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>21681</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2018,7 +2502,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2029,6 +2513,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5034000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>19362</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2064,7 +2564,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2075,6 +2575,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>10656000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>21571</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2110,7 +2626,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2121,6 +2637,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>16688000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>22103</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2156,7 +2688,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2167,6 +2699,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>15783000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>22579</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2202,7 +2750,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2213,6 +2761,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>12770000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>20465</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2248,7 +2812,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2259,6 +2823,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>4838000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>18608</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2294,7 +2874,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2305,6 +2885,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>9740000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>19717</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2340,7 +2936,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2351,6 +2947,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>18183000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>24083</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2386,7 +2998,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2397,6 +3009,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>15620000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>22346</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2432,7 +3060,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2443,6 +3071,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>13574000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20199</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2478,7 +3122,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2489,6 +3133,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4787000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>18412</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2524,7 +3184,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2535,6 +3195,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>9331000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>18889</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2570,7 +3246,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2581,6 +3257,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>16344000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>21648</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2616,7 +3308,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2627,6 +3319,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>14881000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>21289</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2662,7 +3370,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2673,6 +3381,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5872000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>19190</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2708,7 +3432,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2719,6 +3443,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>9236000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>18696</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2754,7 +3494,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2765,6 +3505,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>15871000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>21021</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2800,7 +3556,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2811,6 +3567,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>14721000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>21060</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2846,7 +3618,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2857,6 +3629,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5938000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19405</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2892,7 +3680,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2903,6 +3691,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>9046000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>18312</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2938,7 +3742,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2949,6 +3753,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>17293000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>22905</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2984,7 +3804,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2995,6 +3815,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>14848000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>21242</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3030,7 +3866,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3041,6 +3877,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>5625000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>18382</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3076,7 +3928,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3087,6 +3939,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8847000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>17909</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3122,7 +3990,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3133,6 +4001,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>15540000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>20583</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3168,7 +4052,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3179,6 +4063,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>14699000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>21029</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3229,6 +4129,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3279,6 +4199,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3314,7 +4254,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3325,13 +4265,29 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>23592</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3404,7 +4360,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -3414,7 +4370,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -3545,7 +4501,7 @@
           <t>B | 1296呎 (3房)
 $3874万
 $29,895/呎
-(已售)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -3576,12 +4532,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
-招标单位
--
-(在售)</t>
+$1240万
+$25,107/呎
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3589,7 +4545,7 @@
           <t>D | 260呎 (开放式)
 $624万
 $23,992/呎
-(已售)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -3597,7 +4553,7 @@
           <t>E | 640呎 (3房)
 $1550万
 $24,219/呎
-(已售)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr"/>
@@ -3614,7 +4570,7 @@
           <t>A | 699呎 (3房)
 $1765万
 $25,250/呎
-(已售)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -3630,7 +4586,7 @@
           <t>C | 494呎 (2房)
 $1165万
 $23,589/呎
-(已售)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3638,7 +4594,7 @@
           <t>D | 260呎 (开放式)
 $600万
 $23,077/呎
-(已售)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -3646,7 +4602,7 @@
           <t>E | 640呎 (3房)
 $1483万
 $23,177/呎
-(已售)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr"/>
@@ -3663,7 +4619,7 @@
           <t>A | 699呎 (3房)
 $1667万
 $23,854/呎
-(已售)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -3671,7 +4627,7 @@
           <t>B | 755呎 (3房)
 $1796万
 $23,787/呎
-(已售)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -3679,7 +4635,7 @@
           <t>C | 494呎 (2房)
 $1090万
 $22,065/呎
-(已售)</t>
+(24年-01月-24日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -3687,7 +4643,7 @@
           <t>D | 260呎 (开放式)
 $568万
 $21,846/呎
-(已售)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -3695,7 +4651,7 @@
           <t>E | 640呎 (3房)
 $1305万
 $20,392/呎
-(已售)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr"/>
@@ -3712,7 +4668,7 @@
           <t>A | 699呎 (3房)
 $1634万
 $23,372/呎
-(已售)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -3720,7 +4676,7 @@
           <t>B | 755呎 (3房)
 $1766万
 $23,389/呎
-(已售)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -3728,7 +4684,7 @@
           <t>C | 494呎 (2房)
 $1085万
 $21,964/呎
-(已售)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -3736,7 +4692,7 @@
           <t>D | 260呎 (开放式)
 $516万
 $19,846/呎
-(已售)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -3744,7 +4700,7 @@
           <t>E | 640呎 (3房)
 $1292万
 $20,194/呎
-(已售)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr"/>
@@ -3761,7 +4717,7 @@
           <t>A | 699呎 (3房)
 $1578万
 $22,579/呎
-(已售)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -3769,7 +4725,7 @@
           <t>B | 755呎 (3房)
 $1669万
 $22,103/呎
-(已售)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -3777,7 +4733,7 @@
           <t>C | 494呎 (2房)
 $1066万
 $21,571/呎
-(已售)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -3785,7 +4741,7 @@
           <t>D | 260呎 (开放式)
 $503万
 $19,362/呎
-(已售)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -3793,7 +4749,7 @@
           <t>E | 640呎 (3房)
 $1388万
 $21,681/呎
-(已售)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr"/>
@@ -3810,7 +4766,7 @@
           <t>A | 699呎 (3房)
 $1562万
 $22,346/呎
-(已售)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -3818,7 +4774,7 @@
           <t>B | 755呎 (3房)
 $1818万
 $24,083/呎
-(已售)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -3826,7 +4782,7 @@
           <t>C | 494呎 (2房)
 $974万
 $19,717/呎
-(已售)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -3834,7 +4790,7 @@
           <t>D | 260呎 (开放式)
 $484万
 $18,608/呎
-(已售)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -3842,7 +4798,7 @@
           <t>E | 624呎 (3房)
 $1277万
 $20,465/呎
-(已售)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr"/>
@@ -3859,7 +4815,7 @@
           <t>A | 699呎 (3房)
 $1488万
 $21,289/呎
-(已售)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -3867,7 +4823,7 @@
           <t>B | 755呎 (3房)
 $1634万
 $21,648/呎
-(已售)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -3875,7 +4831,7 @@
           <t>C | 494呎 (2房)
 $933万
 $18,889/呎
-(已售)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -3883,7 +4839,7 @@
           <t>D | 260呎 (开放式)
 $479万
 $18,412/呎
-(已售)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -3891,7 +4847,7 @@
           <t>E | 672呎 (3房)
 $1357万
 $20,199/呎
-(已售)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr"/>
@@ -3908,7 +4864,7 @@
           <t>A | 699呎 (3房)
 $1472万
 $21,060/呎
-(已售)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -3916,7 +4872,7 @@
           <t>B | 755呎 (3房)
 $1587万
 $21,021/呎
-(已售)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -3924,7 +4880,7 @@
           <t>C | 494呎 (2房)
 $924万
 $18,696/呎
-(已售)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -3932,7 +4888,7 @@
           <t>D | 306呎 (1房)
 $587万
 $19,190/呎
-(已售)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr"/>
@@ -3950,7 +4906,7 @@
           <t>A | 699呎 (3房)
 $1485万
 $21,242/呎
-(已售)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -3958,7 +4914,7 @@
           <t>B | 755呎 (3房)
 $1729万
 $22,905/呎
-(已售)</t>
+(24年-01月-25日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -3966,7 +4922,7 @@
           <t>C | 494呎 (2房)
 $905万
 $18,312/呎
-(已售)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -3974,7 +4930,7 @@
           <t>D | 306呎 (1房)
 $594万
 $19,405/呎
-(已售)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr"/>
@@ -3992,7 +4948,7 @@
           <t>A | 699呎 (3房)
 $1470万
 $21,029/呎
-(已售)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -4000,7 +4956,7 @@
           <t>B | 755呎 (3房)
 $1554万
 $20,583/呎
-(已售)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -4008,7 +4964,7 @@
           <t>C | 494呎 (2房)
 $885万
 $17,909/呎
-(已售)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -4016,7 +4972,7 @@
           <t>D | 306呎 (1房)
 $562万
 $18,382/呎
-(已售)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr"/>
@@ -4034,7 +4990,7 @@
           <t>A | 657呎 (3房)
 $1550万
 $23,592/呎
-(已售)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
